--- a/pruebas/excel/datos_ejemplo.xlsx
+++ b/pruebas/excel/datos_ejemplo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,29 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>eee</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>eee</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
